--- a/output/graficos_dimensiones/comunal_d_env_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:17</t>
+    <t xml:space="preserve">2026-09-10 01:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:31</t>
+    <t xml:space="preserve">2026-09-12 22:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_biobio.xlsx
@@ -57,24 +57,24 @@
     <t xml:space="preserve">Concepción</t>
   </si>
   <si>
+    <t xml:space="preserve">Lota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tucapel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tomé</t>
   </si>
   <si>
-    <t xml:space="preserve">Lota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tucapel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Talcahuano</t>
   </si>
   <si>
+    <t xml:space="preserve">Contulmo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hualpén</t>
   </si>
   <si>
-    <t xml:space="preserve">Contulmo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Santa Juana</t>
   </si>
   <si>
@@ -96,12 +96,12 @@
     <t xml:space="preserve">Curanilahue</t>
   </si>
   <si>
+    <t xml:space="preserve">Nacimiento</t>
+  </si>
+  <si>
     <t xml:space="preserve">Negrete</t>
   </si>
   <si>
-    <t xml:space="preserve">Nacimiento</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cabrero</t>
   </si>
   <si>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:42</t>
+    <t xml:space="preserve">2026-09-24 00:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -577,7 +577,7 @@
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>169.09</v>
+        <v>179.31</v>
       </c>
     </row>
     <row r="3">
@@ -594,7 +594,7 @@
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>162.57</v>
+        <v>174.94</v>
       </c>
     </row>
     <row r="4">
@@ -611,7 +611,7 @@
         <v>2021</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>158.37</v>
+        <v>171.45</v>
       </c>
     </row>
     <row r="5">
@@ -628,7 +628,7 @@
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>158.3</v>
+        <v>171.36</v>
       </c>
     </row>
     <row r="6">
@@ -645,7 +645,7 @@
         <v>2021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>151.89</v>
+        <v>164.74</v>
       </c>
     </row>
     <row r="7">
@@ -662,7 +662,7 @@
         <v>2021</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>149.2</v>
+        <v>161.87</v>
       </c>
     </row>
     <row r="8">
@@ -679,7 +679,7 @@
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>141.04</v>
+        <v>151.62</v>
       </c>
     </row>
     <row r="9">
@@ -690,13 +690,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>8111</v>
+        <v>8106</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>139.73</v>
+        <v>151.31</v>
       </c>
     </row>
     <row r="10">
@@ -707,13 +707,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>8106</v>
+        <v>8312</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>139.22</v>
+        <v>150.78</v>
       </c>
     </row>
     <row r="11">
@@ -724,13 +724,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>8312</v>
+        <v>8111</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>138.33</v>
+        <v>150.31</v>
       </c>
     </row>
     <row r="12">
@@ -747,7 +747,7 @@
         <v>2021</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>136.99</v>
+        <v>147.91</v>
       </c>
     </row>
     <row r="13">
@@ -758,13 +758,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>8112</v>
+        <v>8204</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>129.15</v>
+        <v>140.32</v>
       </c>
     </row>
     <row r="14">
@@ -775,13 +775,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>8204</v>
+        <v>8112</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>127.59</v>
+        <v>139.08</v>
       </c>
     </row>
     <row r="15">
@@ -798,7 +798,7 @@
         <v>2021</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>127.25</v>
+        <v>136.11</v>
       </c>
     </row>
     <row r="16">
@@ -815,7 +815,7 @@
         <v>2021</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>124.37</v>
+        <v>135.08</v>
       </c>
     </row>
     <row r="17">
@@ -832,7 +832,7 @@
         <v>2021</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>123.26</v>
+        <v>133.05</v>
       </c>
     </row>
     <row r="18">
@@ -849,7 +849,7 @@
         <v>2021</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>122.62</v>
+        <v>132.33</v>
       </c>
     </row>
     <row r="19">
@@ -866,7 +866,7 @@
         <v>2021</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>121.66</v>
+        <v>132.2</v>
       </c>
     </row>
     <row r="20">
@@ -883,7 +883,7 @@
         <v>2021</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>121</v>
+        <v>130.86</v>
       </c>
     </row>
     <row r="21">
@@ -900,7 +900,7 @@
         <v>2021</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>118.81</v>
+        <v>128.33</v>
       </c>
     </row>
     <row r="22">
@@ -911,13 +911,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>8307</v>
+        <v>8306</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>115.48</v>
+        <v>123.67</v>
       </c>
     </row>
     <row r="23">
@@ -928,13 +928,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>8306</v>
+        <v>8307</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>113.2</v>
+        <v>123.65</v>
       </c>
     </row>
     <row r="24">
@@ -951,7 +951,7 @@
         <v>2021</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>110.16</v>
+        <v>119.66</v>
       </c>
     </row>
     <row r="25">
@@ -968,7 +968,7 @@
         <v>2021</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>104.66</v>
+        <v>113.08</v>
       </c>
     </row>
     <row r="26">
@@ -985,7 +985,7 @@
         <v>2021</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>103.38</v>
+        <v>112.43</v>
       </c>
     </row>
     <row r="27">
@@ -1002,7 +1002,7 @@
         <v>2021</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>100.25</v>
+        <v>107.39</v>
       </c>
     </row>
     <row r="28">
@@ -1019,7 +1019,7 @@
         <v>2021</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>97.3</v>
+        <v>104.85</v>
       </c>
     </row>
     <row r="29">
@@ -1036,7 +1036,7 @@
         <v>2021</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>96.52</v>
+        <v>104.12</v>
       </c>
     </row>
     <row r="30">
@@ -1053,7 +1053,7 @@
         <v>2021</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>93.13</v>
+        <v>100.45</v>
       </c>
     </row>
     <row r="31">
@@ -1070,7 +1070,7 @@
         <v>2021</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>84.2</v>
+        <v>90.86</v>
       </c>
     </row>
     <row r="32">
@@ -1087,7 +1087,7 @@
         <v>2021</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>76.07</v>
+        <v>82.16</v>
       </c>
     </row>
     <row r="33">
@@ -1104,7 +1104,7 @@
         <v>2021</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>74.92</v>
+        <v>80.53</v>
       </c>
     </row>
     <row r="34">
@@ -1121,7 +1121,7 @@
         <v>2021</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>56.67</v>
+        <v>61.98</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:11</t>
+    <t xml:space="preserve">2026-10-02 16:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_biobio.xlsx
@@ -117,13 +117,13 @@
     <t xml:space="preserve">Cañete</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Coronel</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Tirúa</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:26</t>
+    <t xml:space="preserve">2026-10-04 10:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:41</t>
+    <t xml:space="preserve">2026-10-05 16:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
